--- a/artfynd/A 41367-2026 artfynd.xlsx
+++ b/artfynd/A 41367-2026 artfynd.xlsx
@@ -1629,11 +1629,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>

--- a/artfynd/A 41367-2026 artfynd.xlsx
+++ b/artfynd/A 41367-2026 artfynd.xlsx
@@ -1600,7 +1600,7 @@
         <v>130319278</v>
       </c>
       <c r="B10" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
